--- a/static/Sections_timetable_config.xlsx
+++ b/static/Sections_timetable_config.xlsx
@@ -8,8 +8,9 @@
     <sheet name="Courses" sheetId="3" r:id="rId3"/>
     <sheet name="Faculty" sheetId="4" r:id="rId4"/>
     <sheet name="Mapping" sheetId="5" r:id="rId5"/>
-    <sheet name="Constraints" sheetId="6" r:id="rId6"/>
-    <sheet name="Timetable" sheetId="7" r:id="rId7"/>
+    <sheet name="Conflicts" sheetId="6" r:id="rId6"/>
+    <sheet name="Constraints" sheetId="7" r:id="rId7"/>
+    <sheet name="Timetable" sheetId="8" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
@@ -419,7 +420,7 @@
         <v>Exported at</v>
       </c>
       <c r="B2" t="str">
-        <v>6/6/2026, 9:17:31 PM</v>
+        <v>6/26/2026, 10:24:05 PM</v>
       </c>
     </row>
     <row r="3">
@@ -1791,7 +1792,78 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C5"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="2" width="30.83203125" customWidth="1"/>
+    <col min="3" max="3" width="20.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Group</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Courses</v>
+      </c>
+      <c r="C1" t="str">
+        <v>Sections</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="str">
+        <v>EFM-02-A, EFM-03, EIT-01-A, EMM-03-A, EMM-16, EOM-01-C, EOM-02-A, ESM-03</v>
+      </c>
+      <c r="C2" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="str">
+        <v>EEC-03, EFM-01, EFM-12, EMM-02, EMM-14, EOM-01-B, EOM-02-B, ESM-01-A, ESM-02-A</v>
+      </c>
+      <c r="C3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="str">
+        <v>EEC-01, EFM-02-B, EHLM-06, EHR-01, EMM-01, EMM-03-B, EOM-01-A, ESM-01-B, ESM-02-B</v>
+      </c>
+      <c r="C4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="str">
+        <v>EEC-02, EHLM-01, EHLM-02, EIT-01-B, EIT-02</v>
+      </c>
+      <c r="C5" t="str">
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:C5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
   <cols>
     <col min="1" max="1" width="34.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1853,16 +1925,32 @@
         <v>none</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>spreadingRule.enabled</v>
+      </c>
+      <c r="B8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>spreadingRule.weight</v>
+      </c>
+      <c r="B9">
+        <v>0.01</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:J88"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -1922,19 +2010,19 @@
         <v>11:45</v>
       </c>
       <c r="E2" t="str">
-        <v>IS (SD)</v>
+        <v>FM1 (AA)</v>
       </c>
       <c r="F2" t="str">
         <v>OB2 (AK)</v>
       </c>
       <c r="G2" t="str">
-        <v>IS (RVN)</v>
+        <v>EE (AT)</v>
       </c>
       <c r="H2" t="str">
-        <v>OB2 (AJ)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="I2" t="str">
-        <v>IS (KS)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -1954,7 +2042,7 @@
         <v>15:00</v>
       </c>
       <c r="E3" t="str">
-        <v>FM1 (AA)</v>
+        <v>OB2 (RC)</v>
       </c>
       <c r="F3" t="str">
         <v>FM1 (JLPJ)</v>
@@ -1963,10 +2051,10 @@
         <v>OB2 (AK)</v>
       </c>
       <c r="H3" t="str">
-        <v>OR (RK)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="I3" t="str">
-        <v>FM1 (NJ)</v>
+        <v>IS (KS)</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -2001,7 +2089,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>IS (AP)</v>
+        <v>FM1 (SSSK)</v>
       </c>
     </row>
     <row r="5">
@@ -2065,7 +2153,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>EE (AT)</v>
+        <v>OB2 (AK)</v>
       </c>
     </row>
     <row r="7">
@@ -2082,16 +2170,16 @@
         <v>11:45</v>
       </c>
       <c r="E7" t="str">
-        <v>EE (AT)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="F7" t="str">
-        <v>EE (SRN)</v>
+        <v>BL (SN)</v>
       </c>
       <c r="G7" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>IS (RVN)</v>
       </c>
       <c r="H7" t="str">
-        <v>IS (SD)</v>
+        <v>OB2 (AJ)</v>
       </c>
       <c r="I7" t="str">
         <v>OR (RK)</v>
@@ -2114,19 +2202,19 @@
         <v>15:00</v>
       </c>
       <c r="E8" t="str">
-        <v>OB2 (RC)</v>
+        <v>EE (AT)</v>
       </c>
       <c r="F8" t="str">
         <v>OR (RK)</v>
       </c>
       <c r="G8" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (SSSK)</v>
       </c>
       <c r="H8" t="str">
-        <v>EE (LME)</v>
+        <v>BL (DP)</v>
       </c>
       <c r="I8" t="str">
-        <v>BL (SM)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -2178,10 +2266,10 @@
         <v>11:45</v>
       </c>
       <c r="E10" t="str">
-        <v>EE (AT)</v>
+        <v>BL (SN)</v>
       </c>
       <c r="F10" t="str">
-        <v>EE (SRN)</v>
+        <v>IS (SA)</v>
       </c>
       <c r="G10" t="str">
         <v>OR (PNR)</v>
@@ -2190,7 +2278,7 @@
         <v>IS (SD)</v>
       </c>
       <c r="I10" t="str">
-        <v>OR (RK)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -2210,19 +2298,19 @@
         <v>15:00</v>
       </c>
       <c r="E11" t="str">
-        <v>OB2 (RC)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="F11" t="str">
+        <v>EE (SRN)</v>
+      </c>
+      <c r="G11" t="str">
+        <v>IS (RVN)</v>
+      </c>
+      <c r="H11" t="str">
         <v>OR (RK)</v>
       </c>
-      <c r="G11" t="str">
-        <v>FM1 (SSSK)</v>
-      </c>
-      <c r="H11" t="str">
-        <v>EE (LME)</v>
-      </c>
       <c r="I11" t="str">
-        <v>BL (SM)</v>
+        <v>OB2 (AJ)</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -2257,7 +2345,7 @@
         <v/>
       </c>
       <c r="J12" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>IS (AP)</v>
       </c>
     </row>
     <row r="13">
@@ -2289,7 +2377,7 @@
         <v/>
       </c>
       <c r="J13" t="str">
-        <v>OB2 (AK)</v>
+        <v>EE (AT)</v>
       </c>
     </row>
     <row r="14">
@@ -2338,19 +2426,19 @@
         <v>11:45</v>
       </c>
       <c r="E15" t="str">
-        <v>BL (SN)</v>
+        <v>IS (SD)</v>
       </c>
       <c r="F15" t="str">
         <v>FM1 (JLPJ)</v>
       </c>
       <c r="G15" t="str">
-        <v>IS (RVN)</v>
+        <v>OB2 (AK)</v>
       </c>
       <c r="H15" t="str">
-        <v>FM1 (NJ)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="I15" t="str">
-        <v>EE (LME)</v>
+        <v>BL (SM)</v>
       </c>
       <c r="J15" t="str">
         <v/>
@@ -2370,19 +2458,19 @@
         <v>15:00</v>
       </c>
       <c r="E16" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (AA)</v>
       </c>
       <c r="F16" t="str">
-        <v>BL (SN)</v>
+        <v>OB2 (AK)</v>
       </c>
       <c r="G16" t="str">
         <v>EE (AT)</v>
       </c>
       <c r="H16" t="str">
-        <v>OR (RK)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="I16" t="str">
-        <v>FM1 (NJ)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="J16" t="str">
         <v/>
@@ -2417,7 +2505,7 @@
         <v/>
       </c>
       <c r="J17" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (SSSK)</v>
       </c>
     </row>
     <row r="18">
@@ -2434,19 +2522,19 @@
         <v>11:45</v>
       </c>
       <c r="E18" t="str">
-        <v>IS (SD)</v>
+        <v>FM1 (AA)</v>
       </c>
       <c r="F18" t="str">
         <v>OB2 (AK)</v>
       </c>
       <c r="G18" t="str">
-        <v>BL (SM)</v>
+        <v>EE (AT)</v>
       </c>
       <c r="H18" t="str">
-        <v>FM1 (NJ)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="I18" t="str">
-        <v>EE (LME)</v>
+        <v>IS (KS)</v>
       </c>
       <c r="J18" t="str">
         <v/>
@@ -2466,19 +2554,19 @@
         <v>15:00</v>
       </c>
       <c r="E19" t="str">
-        <v>OR (PNR)</v>
+        <v>OB2 (RC)</v>
       </c>
       <c r="F19" t="str">
-        <v>BL (SN)</v>
+        <v>FM1 (JLPJ)</v>
       </c>
       <c r="G19" t="str">
-        <v>EE (AT)</v>
+        <v>BL (SM)</v>
       </c>
       <c r="H19" t="str">
-        <v>BL (DP)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="I19" t="str">
-        <v>FM1 (NJ)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="J19" t="str">
         <v/>
@@ -2513,7 +2601,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>OR (PNR)</v>
+        <v>BL (DP)</v>
       </c>
     </row>
     <row r="21">
@@ -2545,7 +2633,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>BL (DP)</v>
+        <v>OR (PNR)</v>
       </c>
     </row>
     <row r="22">
@@ -2577,7 +2665,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>OB2 (AK)</v>
       </c>
     </row>
     <row r="23">
@@ -2594,19 +2682,19 @@
         <v>11:45</v>
       </c>
       <c r="E23" t="str">
-        <v>EE (AT)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="F23" t="str">
-        <v>OR (RK)</v>
+        <v>BL (SN)</v>
       </c>
       <c r="G23" t="str">
         <v>FM1 (SSSK)</v>
       </c>
       <c r="H23" t="str">
-        <v>EE (LME)</v>
+        <v>OB2 (AJ)</v>
       </c>
       <c r="I23" t="str">
-        <v>IS (KS)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="J23" t="str">
         <v/>
@@ -2626,10 +2714,10 @@
         <v>15:00</v>
       </c>
       <c r="E24" t="str">
-        <v>FM1 (AA)</v>
+        <v>BL (SN)</v>
       </c>
       <c r="F24" t="str">
-        <v>IS (SA)</v>
+        <v>EE (SRN)</v>
       </c>
       <c r="G24" t="str">
         <v>OR (PNR)</v>
@@ -2638,7 +2726,7 @@
         <v>IS (SD)</v>
       </c>
       <c r="I24" t="str">
-        <v>OR (RK)</v>
+        <v>OB2 (AJ)</v>
       </c>
       <c r="J24" t="str">
         <v/>
@@ -2690,19 +2778,19 @@
         <v>11:45</v>
       </c>
       <c r="E26" t="str">
-        <v>EE (AT)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="F26" t="str">
+        <v>IS (SA)</v>
+      </c>
+      <c r="G26" t="str">
+        <v>FM1 (SSSK)</v>
+      </c>
+      <c r="H26" t="str">
         <v>OR (RK)</v>
       </c>
-      <c r="G26" t="str">
-        <v>OB2 (AK)</v>
-      </c>
-      <c r="H26" t="str">
+      <c r="I26" t="str">
         <v>OB2 (AJ)</v>
-      </c>
-      <c r="I26" t="str">
-        <v>BL (SM)</v>
       </c>
       <c r="J26" t="str">
         <v/>
@@ -2722,19 +2810,19 @@
         <v>15:00</v>
       </c>
       <c r="E27" t="str">
-        <v>FM1 (AA)</v>
+        <v>EE (AT)</v>
       </c>
       <c r="F27" t="str">
         <v>EE (SRN)</v>
       </c>
       <c r="G27" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="H27" t="str">
-        <v>IS (SD)</v>
+        <v>OB2 (AJ)</v>
       </c>
       <c r="I27" t="str">
-        <v>IS (KS)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="J27" t="str">
         <v/>
@@ -2769,7 +2857,7 @@
         <v/>
       </c>
       <c r="J28" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>EE (AT)</v>
       </c>
     </row>
     <row r="29">
@@ -2801,7 +2889,7 @@
         <v/>
       </c>
       <c r="J29" t="str">
-        <v>IS (AP)</v>
+        <v>OB2 (AK)</v>
       </c>
     </row>
     <row r="30">
@@ -2833,7 +2921,7 @@
         <v/>
       </c>
       <c r="J30" t="str">
-        <v>OB2 (AK)</v>
+        <v>OR (PNR)</v>
       </c>
     </row>
     <row r="31">
@@ -2850,19 +2938,19 @@
         <v>11:45</v>
       </c>
       <c r="E31" t="str">
-        <v>BL (SN)</v>
+        <v>IS (SD)</v>
       </c>
       <c r="F31" t="str">
-        <v>FM1 (JLPJ)</v>
+        <v>OB2 (AK)</v>
       </c>
       <c r="G31" t="str">
         <v>IS (RVN)</v>
       </c>
       <c r="H31" t="str">
-        <v>OR (RK)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="I31" t="str">
-        <v>OB2 (AJ)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="J31" t="str">
         <v/>
@@ -2882,19 +2970,19 @@
         <v>15:00</v>
       </c>
       <c r="E32" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (AA)</v>
       </c>
       <c r="F32" t="str">
+        <v>OR (RK)</v>
+      </c>
+      <c r="G32" t="str">
         <v>OB2 (AK)</v>
       </c>
-      <c r="G32" t="str">
-        <v>BL (SM)</v>
-      </c>
       <c r="H32" t="str">
+        <v>EE (LME)</v>
+      </c>
+      <c r="I32" t="str">
         <v>FM1 (NJ)</v>
-      </c>
-      <c r="I32" t="str">
-        <v>EE (LME)</v>
       </c>
       <c r="J32" t="str">
         <v/>
@@ -2929,7 +3017,7 @@
         <v/>
       </c>
       <c r="J33" t="str">
-        <v>OR (PNR)</v>
+        <v>BL (DP)</v>
       </c>
     </row>
     <row r="34">
@@ -2946,19 +3034,19 @@
         <v>11:45</v>
       </c>
       <c r="E34" t="str">
-        <v>IS (SD)</v>
+        <v>OB2 (RC)</v>
       </c>
       <c r="F34" t="str">
-        <v>FM1 (JLPJ)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="G34" t="str">
-        <v>IS (RVN)</v>
+        <v>BL (SM)</v>
       </c>
       <c r="H34" t="str">
-        <v>OR (RK)</v>
+        <v>BL (DP)</v>
       </c>
       <c r="I34" t="str">
-        <v>EE (LME)</v>
+        <v>IS (KS)</v>
       </c>
       <c r="J34" t="str">
         <v/>
@@ -2978,19 +3066,19 @@
         <v>15:00</v>
       </c>
       <c r="E35" t="str">
-        <v>OB2 (RC)</v>
+        <v>IS (SD)</v>
       </c>
       <c r="F35" t="str">
-        <v>OB2 (AK)</v>
+        <v>FM1 (JLPJ)</v>
       </c>
       <c r="G35" t="str">
         <v>EE (AT)</v>
       </c>
       <c r="H35" t="str">
+        <v>EE (LME)</v>
+      </c>
+      <c r="I35" t="str">
         <v>FM1 (NJ)</v>
-      </c>
-      <c r="I35" t="str">
-        <v>OB2 (AJ)</v>
       </c>
       <c r="J35" t="str">
         <v/>
@@ -3025,7 +3113,7 @@
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>EE (AT)</v>
+        <v>FM1 (SSSK)</v>
       </c>
     </row>
     <row r="37">
@@ -3057,7 +3145,7 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>OB2 (AK)</v>
+        <v>OR (PNR)</v>
       </c>
     </row>
     <row r="38">
@@ -3089,7 +3177,7 @@
         <v/>
       </c>
       <c r="J38" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>EE (AT)</v>
       </c>
     </row>
     <row r="39">
@@ -3106,19 +3194,19 @@
         <v>11:45</v>
       </c>
       <c r="E39" t="str">
-        <v>FM1 (AA)</v>
+        <v>EE (AT)</v>
       </c>
       <c r="F39" t="str">
-        <v>BL (SN)</v>
+        <v>EE (SRN)</v>
       </c>
       <c r="G39" t="str">
         <v>OR (PNR)</v>
       </c>
       <c r="H39" t="str">
-        <v>EE (LME)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="I39" t="str">
-        <v>FM1 (NJ)</v>
+        <v>OB2 (AJ)</v>
       </c>
       <c r="J39" t="str">
         <v/>
@@ -3138,10 +3226,10 @@
         <v>15:00</v>
       </c>
       <c r="E40" t="str">
-        <v>EE (AT)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="F40" t="str">
-        <v>EE (SRN)</v>
+        <v>IS (SA)</v>
       </c>
       <c r="G40" t="str">
         <v>FM1 (SSSK)</v>
@@ -3185,7 +3273,7 @@
         <v/>
       </c>
       <c r="J41" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>IS (AP)</v>
       </c>
     </row>
     <row r="42">
@@ -3202,19 +3290,19 @@
         <v>11:45</v>
       </c>
       <c r="E42" t="str">
-        <v>FM1 (AA)</v>
+        <v>EE (AT)</v>
       </c>
       <c r="F42" t="str">
         <v>EE (SRN)</v>
       </c>
       <c r="G42" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="H42" t="str">
-        <v>EE (LME)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="I42" t="str">
-        <v>FM1 (NJ)</v>
+        <v>OB2 (AJ)</v>
       </c>
       <c r="J42" t="str">
         <v/>
@@ -3234,16 +3322,16 @@
         <v>15:00</v>
       </c>
       <c r="E43" t="str">
-        <v>EE (AT)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="F43" t="str">
-        <v>BL (SN)</v>
+        <v>IS (SA)</v>
       </c>
       <c r="G43" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (SSSK)</v>
       </c>
       <c r="H43" t="str">
-        <v>BL (DP)</v>
+        <v>IS (SD)</v>
       </c>
       <c r="I43" t="str">
         <v>OR (RK)</v>
@@ -3281,7 +3369,7 @@
         <v/>
       </c>
       <c r="J44" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>OB2 (AK)</v>
       </c>
     </row>
     <row r="45">
@@ -3313,7 +3401,7 @@
         <v/>
       </c>
       <c r="J45" t="str">
-        <v>IS (AP)</v>
+        <v>EE (AT)</v>
       </c>
     </row>
     <row r="46">
@@ -3345,7 +3433,7 @@
         <v/>
       </c>
       <c r="J46" t="str">
-        <v>EE (AT)</v>
+        <v>FM1 (SSSK)</v>
       </c>
     </row>
     <row r="47">
@@ -3362,19 +3450,19 @@
         <v>11:45</v>
       </c>
       <c r="E47" t="str">
-        <v>IS (SD)</v>
+        <v>OB2 (RC)</v>
       </c>
       <c r="F47" t="str">
-        <v>IS (SA)</v>
+        <v>FM1 (JLPJ)</v>
       </c>
       <c r="G47" t="str">
-        <v>OB2 (AK)</v>
+        <v>IS (RVN)</v>
       </c>
       <c r="H47" t="str">
-        <v>OR (RK)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="I47" t="str">
-        <v>IS (KS)</v>
+        <v>BL (SM)</v>
       </c>
       <c r="J47" t="str">
         <v/>
@@ -3394,7 +3482,7 @@
         <v>15:00</v>
       </c>
       <c r="E48" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (AA)</v>
       </c>
       <c r="F48" t="str">
         <v>OR (RK)</v>
@@ -3403,10 +3491,10 @@
         <v>EE (AT)</v>
       </c>
       <c r="H48" t="str">
-        <v>OB2 (AJ)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="I48" t="str">
-        <v>BL (SM)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="J48" t="str">
         <v/>
@@ -3441,7 +3529,7 @@
         <v/>
       </c>
       <c r="J49" t="str">
-        <v>BL (DP)</v>
+        <v>OR (PNR)</v>
       </c>
     </row>
     <row r="50">
@@ -3464,13 +3552,13 @@
         <v>OR (RK)</v>
       </c>
       <c r="G50" t="str">
-        <v>OB2 (AK)</v>
+        <v>EE (AT)</v>
       </c>
       <c r="H50" t="str">
         <v>OB2 (AJ)</v>
       </c>
       <c r="I50" t="str">
-        <v>IS (KS)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="J50" t="str">
         <v/>
@@ -3490,19 +3578,19 @@
         <v>15:00</v>
       </c>
       <c r="E51" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (AA)</v>
       </c>
       <c r="F51" t="str">
-        <v>IS (SA)</v>
+        <v>BL (SN)</v>
       </c>
       <c r="G51" t="str">
-        <v>EE (AT)</v>
+        <v>BL (SM)</v>
       </c>
       <c r="H51" t="str">
-        <v>OR (RK)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="I51" t="str">
-        <v>OB2 (AJ)</v>
+        <v>IS (KS)</v>
       </c>
       <c r="J51" t="str">
         <v/>
@@ -3537,7 +3625,7 @@
         <v/>
       </c>
       <c r="J52" t="str">
-        <v>EE (AT)</v>
+        <v>OR (PNR)</v>
       </c>
     </row>
     <row r="53">
@@ -3569,7 +3657,7 @@
         <v/>
       </c>
       <c r="J53" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (SSSK)</v>
       </c>
     </row>
     <row r="54">
@@ -3601,7 +3689,7 @@
         <v/>
       </c>
       <c r="J54" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>IS (AP)</v>
       </c>
     </row>
     <row r="55">
@@ -3618,19 +3706,19 @@
         <v>11:45</v>
       </c>
       <c r="E55" t="str">
-        <v>OB2 (RC)</v>
+        <v>EE (AT)</v>
       </c>
       <c r="F55" t="str">
         <v>OB2 (AK)</v>
       </c>
       <c r="G55" t="str">
-        <v>BL (SM)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="H55" t="str">
+        <v>OR (RK)</v>
+      </c>
+      <c r="I55" t="str">
         <v>FM1 (NJ)</v>
-      </c>
-      <c r="I55" t="str">
-        <v>EE (LME)</v>
       </c>
       <c r="J55" t="str">
         <v/>
@@ -3650,19 +3738,19 @@
         <v>15:00</v>
       </c>
       <c r="E56" t="str">
-        <v>FM1 (AA)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="F56" t="str">
-        <v>FM1 (JLPJ)</v>
+        <v>EE (SRN)</v>
       </c>
       <c r="G56" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (SSSK)</v>
       </c>
       <c r="H56" t="str">
-        <v>EE (LME)</v>
+        <v>BL (DP)</v>
       </c>
       <c r="I56" t="str">
-        <v>FM1 (NJ)</v>
+        <v>OB2 (AJ)</v>
       </c>
       <c r="J56" t="str">
         <v/>
@@ -3697,7 +3785,7 @@
         <v/>
       </c>
       <c r="J57" t="str">
-        <v>OB2 (AK)</v>
+        <v>EE (AT)</v>
       </c>
     </row>
     <row r="58">
@@ -3714,19 +3802,19 @@
         <v>11:45</v>
       </c>
       <c r="E58" t="str">
-        <v>OB2 (RC)</v>
+        <v>BL (SN)</v>
       </c>
       <c r="F58" t="str">
-        <v>FM1 (JLPJ)</v>
+        <v>EE (SRN)</v>
       </c>
       <c r="G58" t="str">
-        <v>IS (RVN)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="H58" t="str">
-        <v>FM1 (NJ)</v>
+        <v>IS (SD)</v>
       </c>
       <c r="I58" t="str">
-        <v>EE (LME)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="J58" t="str">
         <v/>
@@ -3749,13 +3837,13 @@
         <v>EE (AT)</v>
       </c>
       <c r="F59" t="str">
+        <v>IS (SA)</v>
+      </c>
+      <c r="G59" t="str">
         <v>OB2 (AK)</v>
       </c>
-      <c r="G59" t="str">
-        <v>OR (PNR)</v>
-      </c>
       <c r="H59" t="str">
-        <v>BL (DP)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="I59" t="str">
         <v>FM1 (NJ)</v>
@@ -3793,7 +3881,7 @@
         <v/>
       </c>
       <c r="J60" t="str">
-        <v>IS (AP)</v>
+        <v>BL (DP)</v>
       </c>
     </row>
     <row r="61">
@@ -3825,7 +3913,7 @@
         <v/>
       </c>
       <c r="J61" t="str">
-        <v>OB2 (AK)</v>
+        <v>IS (AP)</v>
       </c>
     </row>
     <row r="62">
@@ -3857,7 +3945,7 @@
         <v/>
       </c>
       <c r="J62" t="str">
-        <v>BL (DP)</v>
+        <v>FM1 (SSSK)</v>
       </c>
     </row>
     <row r="63">
@@ -3874,19 +3962,19 @@
         <v>11:45</v>
       </c>
       <c r="E63" t="str">
-        <v>OR (PNR)</v>
+        <v>OB2 (RC)</v>
       </c>
       <c r="F63" t="str">
-        <v>IS (SA)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="G63" t="str">
-        <v>EE (AT)</v>
+        <v>BL (SM)</v>
       </c>
       <c r="H63" t="str">
         <v>OB2 (AJ)</v>
       </c>
       <c r="I63" t="str">
-        <v>OR (RK)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="J63" t="str">
         <v/>
@@ -3906,19 +3994,19 @@
         <v>15:00</v>
       </c>
       <c r="E64" t="str">
-        <v>IS (SD)</v>
+        <v>FM1 (AA)</v>
       </c>
       <c r="F64" t="str">
-        <v>EE (SRN)</v>
+        <v>FM1 (JLPJ)</v>
       </c>
       <c r="G64" t="str">
-        <v>OB2 (AK)</v>
+        <v>IS (RVN)</v>
       </c>
       <c r="H64" t="str">
-        <v>OR (RK)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="I64" t="str">
-        <v>OB2 (AJ)</v>
+        <v>BL (SM)</v>
       </c>
       <c r="J64" t="str">
         <v/>
@@ -3953,7 +4041,7 @@
         <v/>
       </c>
       <c r="J65" t="str">
-        <v>OR (PNR)</v>
+        <v>OB2 (AK)</v>
       </c>
     </row>
     <row r="66">
@@ -3970,19 +4058,19 @@
         <v>11:45</v>
       </c>
       <c r="E66" t="str">
-        <v>OR (PNR)</v>
+        <v>OB2 (RC)</v>
       </c>
       <c r="F66" t="str">
-        <v>IS (SA)</v>
+        <v>FM1 (JLPJ)</v>
       </c>
       <c r="G66" t="str">
         <v>EE (AT)</v>
       </c>
       <c r="H66" t="str">
-        <v>OB2 (AJ)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="I66" t="str">
-        <v>OR (RK)</v>
+        <v>IS (KS)</v>
       </c>
       <c r="J66" t="str">
         <v/>
@@ -4002,19 +4090,19 @@
         <v>15:00</v>
       </c>
       <c r="E67" t="str">
-        <v>BL (SN)</v>
+        <v>IS (SD)</v>
       </c>
       <c r="F67" t="str">
-        <v>EE (SRN)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="G67" t="str">
-        <v>OB2 (AK)</v>
+        <v>IS (RVN)</v>
       </c>
       <c r="H67" t="str">
-        <v>OR (RK)</v>
+        <v>OB2 (AJ)</v>
       </c>
       <c r="I67" t="str">
-        <v>OB2 (AJ)</v>
+        <v>BL (SM)</v>
       </c>
       <c r="J67" t="str">
         <v/>
@@ -4049,7 +4137,7 @@
         <v/>
       </c>
       <c r="J68" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (SSSK)</v>
       </c>
     </row>
     <row r="69">
@@ -4081,7 +4169,7 @@
         <v/>
       </c>
       <c r="J69" t="str">
-        <v>BL (DP)</v>
+        <v>OR (PNR)</v>
       </c>
     </row>
     <row r="70">
@@ -4130,19 +4218,19 @@
         <v>11:45</v>
       </c>
       <c r="E71" t="str">
-        <v>OB2 (RC)</v>
+        <v>EE (AT)</v>
       </c>
       <c r="F71" t="str">
+        <v>OB2 (AK)</v>
+      </c>
+      <c r="G71" t="str">
+        <v>FM1 (SSSK)</v>
+      </c>
+      <c r="H71" t="str">
         <v>OR (RK)</v>
       </c>
-      <c r="G71" t="str">
-        <v>OR (PNR)</v>
-      </c>
-      <c r="H71" t="str">
-        <v>EE (LME)</v>
-      </c>
       <c r="I71" t="str">
-        <v>IS (KS)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="J71" t="str">
         <v/>
@@ -4162,19 +4250,19 @@
         <v>15:00</v>
       </c>
       <c r="E72" t="str">
-        <v>FM1 (AA)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="F72" t="str">
-        <v>FM1 (JLPJ)</v>
+        <v>BL (SN)</v>
       </c>
       <c r="G72" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>OB2 (AK)</v>
       </c>
       <c r="H72" t="str">
-        <v>FM1 (NJ)</v>
+        <v>IS (SD)</v>
       </c>
       <c r="I72" t="str">
-        <v>EE (LME)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="J72" t="str">
         <v/>
@@ -4226,19 +4314,19 @@
         <v>11:45</v>
       </c>
       <c r="E74" t="str">
-        <v>FM1 (AA)</v>
+        <v>BL (SN)</v>
       </c>
       <c r="F74" t="str">
+        <v>IS (SA)</v>
+      </c>
+      <c r="G74" t="str">
+        <v>OB2 (AK)</v>
+      </c>
+      <c r="H74" t="str">
+        <v>BL (DP)</v>
+      </c>
+      <c r="I74" t="str">
         <v>OR (RK)</v>
-      </c>
-      <c r="G74" t="str">
-        <v>BL (SM)</v>
-      </c>
-      <c r="H74" t="str">
-        <v>FM1 (NJ)</v>
-      </c>
-      <c r="I74" t="str">
-        <v>EE (LME)</v>
       </c>
       <c r="J74" t="str">
         <v/>
@@ -4261,13 +4349,13 @@
         <v>EE (AT)</v>
       </c>
       <c r="F75" t="str">
-        <v>FM1 (JLPJ)</v>
+        <v>EE (SRN)</v>
       </c>
       <c r="G75" t="str">
         <v>FM1 (SSSK)</v>
       </c>
       <c r="H75" t="str">
-        <v>EE (LME)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="I75" t="str">
         <v>FM1 (NJ)</v>
@@ -4305,7 +4393,7 @@
         <v/>
       </c>
       <c r="J76" t="str">
-        <v>FM1 (SSSK)</v>
+        <v>IS (AP)</v>
       </c>
     </row>
     <row r="77">
@@ -4337,7 +4425,7 @@
         <v/>
       </c>
       <c r="J77" t="str">
-        <v>EE (AT)</v>
+        <v>BL (DP)</v>
       </c>
     </row>
     <row r="78">
@@ -4369,7 +4457,7 @@
         <v/>
       </c>
       <c r="J78" t="str">
-        <v>OB2 (AK)</v>
+        <v>FM1 (SSSK)</v>
       </c>
     </row>
     <row r="79">
@@ -4386,19 +4474,19 @@
         <v>11:45</v>
       </c>
       <c r="E79" t="str">
-        <v>BL (SN)</v>
+        <v>IS (SD)</v>
       </c>
       <c r="F79" t="str">
-        <v>IS (SA)</v>
+        <v>OR (RK)</v>
       </c>
       <c r="G79" t="str">
-        <v>IS (RVN)</v>
+        <v>OR (PNR)</v>
       </c>
       <c r="H79" t="str">
-        <v>BL (DP)</v>
+        <v>FM1 (NJ)</v>
       </c>
       <c r="I79" t="str">
-        <v>OR (RK)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="J79" t="str">
         <v/>
@@ -4418,19 +4506,19 @@
         <v>15:00</v>
       </c>
       <c r="E80" t="str">
-        <v>OR (PNR)</v>
+        <v>FM1 (AA)</v>
       </c>
       <c r="F80" t="str">
-        <v>EE (SRN)</v>
+        <v>FM1 (JLPJ)</v>
       </c>
       <c r="G80" t="str">
         <v>EE (AT)</v>
       </c>
       <c r="H80" t="str">
-        <v>IS (SD)</v>
+        <v>EE (LME)</v>
       </c>
       <c r="I80" t="str">
-        <v>OB2 (AJ)</v>
+        <v>IS (KS)</v>
       </c>
       <c r="J80" t="str">
         <v/>
@@ -4465,7 +4553,7 @@
         <v/>
       </c>
       <c r="J81" t="str">
-        <v>IS (AP)</v>
+        <v>OB2 (AK)</v>
       </c>
     </row>
     <row r="85">
@@ -4473,10 +4561,10 @@
         <v>__META__</v>
       </c>
       <c r="B85" t="str">
-        <v>Generated At</v>
+        <v>Status</v>
       </c>
       <c r="C85" t="str">
-        <v>2026-06-06T21:15:36.650719</v>
+        <v>Feasible</v>
       </c>
     </row>
     <row r="86">
@@ -4484,10 +4572,10 @@
         <v>__META__</v>
       </c>
       <c r="B86" t="str">
-        <v>Constraint</v>
+        <v>Generated At</v>
       </c>
       <c r="C86" t="str">
-        <v>soft</v>
+        <v>2026-06-26T16:53:50.708Z</v>
       </c>
     </row>
     <row r="87">
@@ -4495,15 +4583,26 @@
         <v>__META__</v>
       </c>
       <c r="B87" t="str">
+        <v>Constraint</v>
+      </c>
+      <c r="C87" t="str">
+        <v>soft</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="str">
+        <v>__META__</v>
+      </c>
+      <c r="B88" t="str">
         <v>Penalty</v>
       </c>
-      <c r="C87">
-        <v>0</v>
+      <c r="C88">
+        <v>0.49</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J87"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J88"/>
   </ignoredErrors>
 </worksheet>
 </file>